--- a/data/trans_dic/P20D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,98; 100,0</t>
+          <t>58,95; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 88,02</t>
+          <t>4,64; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,68; 93,98</t>
+          <t>58,11; 95,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,69; 100,0</t>
+          <t>30,26; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,43</t>
+          <t>0,0; 11,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 60,69</t>
+          <t>14,04; 56,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,2; 85,49</t>
+          <t>33,24; 85,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,72</t>
+          <t>0,0; 57,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,48; 71,56</t>
+          <t>28,79; 72,68</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,57; 86,95</t>
+          <t>41,01; 86,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,56; 77,51</t>
+          <t>25,29; 76,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,82; 78,27</t>
+          <t>40,45; 77,01</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,11; 85,06</t>
+          <t>35,48; 85,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,52; 62,29</t>
+          <t>22,68; 62,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,24; 69,68</t>
+          <t>33,68; 69,34</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,94; 92,49</t>
+          <t>37,24; 90,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,07; 90,42</t>
+          <t>37,5; 90,29</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,54; 80,67</t>
+          <t>58,73; 80,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,85; 53,39</t>
+          <t>28,45; 54,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,38; 65,4</t>
+          <t>47,69; 65,39</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9080; 13357</t>
+          <t>7874; 13357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148; 2824</t>
+          <t>149; 3208</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9224; 15568</t>
+          <t>9626; 15803</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1767; 6881</t>
+          <t>2082; 6881</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 991</t>
+          <t>0; 950</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2089; 9018</t>
+          <t>2086; 8348</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5064; 12300</t>
+          <t>4783; 12276</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2830</t>
+          <t>0; 2532</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5342; 13424</t>
+          <t>5400; 13634</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5523; 12453</t>
+          <t>5873; 12357</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2095; 6894</t>
+          <t>2249; 6804</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9708; 18171</t>
+          <t>9392; 17878</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4369; 10895</t>
+          <t>4544; 10914</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3176; 8411</t>
+          <t>3062; 8433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9799; 18333</t>
+          <t>8861; 18245</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 402</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3768; 9186</t>
+          <t>3698; 9019</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3561; 9451</t>
+          <t>3919; 9437</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>36456; 50242</t>
+          <t>36577; 50411</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13339; 25565</t>
+          <t>13623; 26106</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53292; 72047</t>
+          <t>52533; 72037</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,95; 100,0</t>
+          <t>64,7; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 100,0</t>
+          <t>9,96; 82,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,11; 95,4</t>
+          <t>60,05; 94,34</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 100,0</t>
+          <t>27,8; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,91</t>
+          <t>0,0; 37,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 56,18</t>
+          <t>18,07; 61,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,24; 85,33</t>
+          <t>43,23; 89,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,92</t>
+          <t>0,0; 60,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,79; 72,68</t>
+          <t>33,85; 76,36</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,01; 86,28</t>
+          <t>43,14; 88,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,29; 76,5</t>
+          <t>29,47; 78,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,45; 77,01</t>
+          <t>42,07; 77,64</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,48; 85,21</t>
+          <t>32,58; 84,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,68; 62,45</t>
+          <t>26,22; 65,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,68; 69,34</t>
+          <t>35,61; 67,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,24; 90,82</t>
+          <t>40,17; 92,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,5; 90,29</t>
+          <t>35,89; 90,49</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,73; 80,95</t>
+          <t>61,02; 82,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,45; 54,52</t>
+          <t>29,83; 54,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47,69; 65,39</t>
+          <t>49,48; 66,59</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>14461</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7874; 13357</t>
+          <t>9010; 13925</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>149; 3208</t>
+          <t>376; 3130</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9626; 15803</t>
+          <t>10632; 16702</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>677</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>6379</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2082; 6881</t>
+          <t>2146; 7717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 950</t>
+          <t>0; 3708</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2086; 8348</t>
+          <t>3165; 10841</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>12744</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4783; 12276</t>
+          <t>7634; 15868</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2532</t>
+          <t>0; 2863</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5400; 13634</t>
+          <t>7573; 17081</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>15415</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5873; 12357</t>
+          <t>6228; 12735</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2249; 6804</t>
+          <t>3104; 8303</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9392; 17878</t>
+          <t>10506; 19387</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>15524</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4544; 10914</t>
+          <t>4548; 11797</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3062; 8433</t>
+          <t>4073; 10130</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8861; 18245</t>
+          <t>10503; 19914</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7346</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3698; 9019</t>
+          <t>4342; 9956</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3919; 9437</t>
+          <t>4061; 10240</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>71869</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>36577; 50411</t>
+          <t>41618; 56405</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13623; 26106</t>
+          <t>16459; 30027</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52533; 72037</t>
+          <t>61038; 82148</t>
         </is>
       </c>
     </row>
